--- a/public/data/driver_templates_expanded.xlsx
+++ b/public/data/driver_templates_expanded.xlsx
@@ -472,7 +472,7 @@
         <v>DRV-001</v>
       </c>
       <c r="B2" t="str">
-        <v>OH1668243</v>
+        <v>OH0000075</v>
       </c>
       <c r="C2" t="str">
         <v>2024-01-15</v>
@@ -505,7 +505,7 @@
         <v>OH</v>
       </c>
       <c r="M2" t="str">
-        <v>OH441134921</v>
+        <v>OH000000097</v>
       </c>
       <c r="N2" t="str">
         <v>2024-01-15</v>
